--- a/Docs/Prueba Septiembre 1/Insumos/1-Promoambiental/RecaudosReversados_to_date01092026ddMMyyyy_to_date15092026ddMMyyyy___20269161644659.xlsx
+++ b/Docs/Prueba Septiembre 1/Insumos/1-Promoambiental/RecaudosReversados_to_date01092026ddMMyyyy_to_date15092026ddMMyyyy___20269161644659.xlsx
@@ -1,14 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kumo2-my.sharepoint.com/personal/lechaparro_fntecnologia_com/Documents/Proyectos/AAA/2026/08/Automatización/Docs/Prueba Septiembre 1/Insumos/1-Promoambiental/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_5A618399BBB53B22A2FC606A7E1C60E535B43AFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20E3AC5C-39BE-4ECA-9728-CA38A7BA4254}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="30">
   <si>
     <t>Banco</t>
   </si>
@@ -103,47 +115,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0"/>
-    <numFmt numFmtId="165" formatCode="\ dd\/mm\/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="\ dd\/mm\/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="ARIAL"/>
-      <family val="0"/>
       <charset val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="ARIAL"/>
-      <family val="0"/>
-      <charset val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="ARIAL"/>
-      <family val="0"/>
-      <charset val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="ARIAL"/>
-      <family val="0"/>
-      <charset val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="ARIAL"/>
-      <family val="0"/>
-      <charset val="1"/>
-      <color rgb="00000000"/>
     </font>
   </fonts>
   <fills count="2">
@@ -151,816 +132,1083 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="00000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0">
-      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/Sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:F64"/>
-  <sheetFormatPr defaultColWidth="6.86" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="6.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="6.86" style="0" customWidth="1"/>
+    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>46276</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>-26400</v>
       </c>
     </row>
-    <row r="4" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>46276</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>-148570</v>
       </c>
     </row>
-    <row r="5" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>7</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>46276</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>-484630</v>
       </c>
     </row>
-    <row r="6" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>46276</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>-168480</v>
       </c>
     </row>
-    <row r="7" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>26</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>46276</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>-2424830</v>
       </c>
     </row>
-    <row r="8" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>46276</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>-65910</v>
       </c>
     </row>
-    <row r="9" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>46276</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>-42950</v>
       </c>
     </row>
-    <row r="10" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>46276</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>-101180</v>
       </c>
     </row>
-    <row r="11" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>-3462950</v>
       </c>
     </row>
-    <row r="12" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>46275</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>-83310</v>
       </c>
     </row>
-    <row r="14" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>46275</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>46197</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>83310</v>
       </c>
     </row>
-    <row r="15" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>-3462950</v>
       </c>
     </row>
-    <row r="18" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="E26" s="1" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="D27" s="1" t="s">
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C28" s="1" t="s">
+      <c r="E27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>-26400</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="3">
         <v>-26400</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="3">
         <v>-26400</v>
       </c>
     </row>
-    <row r="29" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B29" s="1" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="4">
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="3">
         <v>-26400</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="3">
         <v>-26400</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="3">
         <v>-26400</v>
       </c>
     </row>
-    <row r="30" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C30" s="1" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>-146817.29</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="3">
         <v>-146817.29</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="3">
         <v>-146817.29</v>
       </c>
     </row>
-    <row r="31" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C31" s="1" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>-1752.71</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="3">
         <v>-1752.71</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="3">
         <v>-1752.71</v>
       </c>
     </row>
-    <row r="32" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B32" s="1" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="4">
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="3">
         <v>-148570</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <v>-148570</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="3">
         <v>-148570</v>
       </c>
     </row>
-    <row r="33" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C33" s="1" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="3">
         <v>-484630</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="3">
         <v>-484630</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="3">
         <v>-484630</v>
       </c>
     </row>
-    <row r="34" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="4">
+      <c r="C34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="3">
         <v>-484630</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="3">
         <v>-484630</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="3">
         <v>-484630</v>
       </c>
     </row>
-    <row r="35" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C35" s="1" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>-168480</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="3">
         <v>-168480</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="3">
         <v>-168480</v>
       </c>
     </row>
-    <row r="36" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B36" s="1" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="4">
+      <c r="C36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="3">
         <v>-168480</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="3">
         <v>-168480</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="3">
         <v>-168480</v>
       </c>
     </row>
-    <row r="37" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C37" s="1" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
         <v>23</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="3">
         <v>-2424830</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="3">
         <v>-2424830</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="3">
         <v>-2424830</v>
       </c>
     </row>
-    <row r="38" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="4">
+      <c r="C38" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="3">
         <v>-2424830</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="3">
         <v>-2424830</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="3">
         <v>-2424830</v>
       </c>
     </row>
-    <row r="39" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C39" s="1" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="3">
         <v>-65910</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="3">
         <v>-65910</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="3">
         <v>-65910</v>
       </c>
     </row>
-    <row r="40" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="4">
+      <c r="C40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="3">
         <v>-65910</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="3">
         <v>-65910</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="3">
         <v>-65910</v>
       </c>
     </row>
-    <row r="41" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C41" s="1" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>-42950</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="3">
         <v>-42950</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="3">
         <v>-42950</v>
       </c>
     </row>
-    <row r="42" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B42" s="1" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="4">
+      <c r="C42" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="3">
         <v>-42950</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="3">
         <v>-42950</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="3">
         <v>-42950</v>
       </c>
     </row>
-    <row r="43" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C43" s="1" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="3">
         <v>-101180</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="3">
         <v>-101180</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="3">
         <v>-101180</v>
       </c>
     </row>
-    <row r="44" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="4">
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="3">
         <v>-101180</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="3">
         <v>-101180</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="3">
         <v>-101180</v>
       </c>
     </row>
-    <row r="45" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="4">
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="3">
         <v>-3462950</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="3">
         <v>-3462950</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="3">
         <v>-3462950</v>
       </c>
     </row>
-    <row r="46" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C46" s="1" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="3">
         <v>42680</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="3">
         <v>42680</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="3">
         <v>42680</v>
       </c>
     </row>
-    <row r="47" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C47" s="1" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="3">
         <v>40630</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="3">
         <v>40630</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="3">
         <v>40630</v>
       </c>
     </row>
-    <row r="48" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="C48" s="1" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
         <v>23</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="3">
         <v>-83310</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="3">
         <v>-83310</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="3">
         <v>-83310</v>
       </c>
     </row>
-    <row r="49" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="4">
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="3">
         <v>0</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="3">
         <v>0</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>15</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="4">
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="3">
         <v>0</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="3">
         <v>0</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" s="4">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="3">
         <v>-3462950</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="3">
         <v>-3462950</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="3">
         <v>-3462950</v>
       </c>
     </row>
-    <row r="57" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="58" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B58" s="1" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
         <v>28</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>29</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="B59" s="1" t="s">
+      <c r="D58" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="60" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A60" s="1" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>42680</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="1">
         <v>0</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="1">
         <v>42680</v>
       </c>
     </row>
-    <row r="61" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>26</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="1">
         <v>40630</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="1">
         <v>0</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="1">
         <v>40630</v>
       </c>
     </row>
-    <row r="62" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>23</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="1">
         <v>-83310</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="1">
         <v>-3461197.29</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="1">
         <v>-3544507.29</v>
       </c>
     </row>
-    <row r="63" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="1">
         <v>0</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="1">
         <v>-1752.71</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="1">
         <v>-1752.71</v>
       </c>
     </row>
-    <row r="64" ht="12.75" customHeight="1" outlineLevel="0">
-      <c r="A64" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B64" s="2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>21</v>
+      </c>
+      <c r="B64" s="1">
         <v>0</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="1">
         <v>-3462950</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="1">
         <v>-3462950</v>
       </c>
     </row>
@@ -968,4 +1216,10 @@
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="0" scale="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{4e8ad5fd-3b35-462b-bf95-8eacd4641ce5}" enabled="0" method="" siteId="{4e8ad5fd-3b35-462b-bf95-8eacd4641ce5}" removed="1"/>
+</clbl:labelList>
 </file>